--- a/test_bom_upload.xlsx
+++ b/test_bom_upload.xlsx
@@ -1,40 +1,1208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="100" iterateDelta="0.001"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="270">
+  <si>
+    <t>物料编码</t>
+  </si>
+  <si>
+    <t>位号</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>0010050171</t>
+  </si>
+  <si>
+    <t>C84,C167,C171,C310</t>
+  </si>
+  <si>
+    <t>0010050172</t>
+  </si>
+  <si>
+    <t>0010050225</t>
+  </si>
+  <si>
+    <t>C196,C414,C416</t>
+  </si>
+  <si>
+    <t>0010050168</t>
+  </si>
+  <si>
+    <t>C212,C298,C299</t>
+  </si>
+  <si>
+    <t>0010050173</t>
+  </si>
+  <si>
+    <t>C44,C93</t>
+  </si>
+  <si>
+    <t>0010050220</t>
+  </si>
+  <si>
+    <t>C161</t>
+  </si>
+  <si>
+    <t>0010050175</t>
+  </si>
+  <si>
+    <t>C207</t>
+  </si>
+  <si>
+    <t>0010050185</t>
+  </si>
+  <si>
+    <t>C412,C413</t>
+  </si>
+  <si>
+    <t>0010050183</t>
+  </si>
+  <si>
+    <t>C210,C219</t>
+  </si>
+  <si>
+    <t>0010050248</t>
+  </si>
+  <si>
+    <t>C182,C189,C284</t>
+  </si>
+  <si>
+    <t>0010050247</t>
+  </si>
+  <si>
+    <t>C183,C190,C227,C285</t>
+  </si>
+  <si>
+    <t>0010050246</t>
+  </si>
+  <si>
+    <t>C186,C191,C286</t>
+  </si>
+  <si>
+    <t>0010050245</t>
+  </si>
+  <si>
+    <t>C192,C199,C200,C206,C215,C228,C229</t>
+  </si>
+  <si>
+    <t>0010050160</t>
+  </si>
+  <si>
+    <t>C56,C94,C95,C98,C355,C356,C367,C371</t>
+  </si>
+  <si>
+    <t>0010050115</t>
+  </si>
+  <si>
+    <t>C7,C13,C14,C15,C19,C20,C23,C28,C30,C36,C48,C51,C52,C57,C60,C63,C65,C66,C73,C77,C80,C88,C89,C99,C105,C107,C110,C135,C141,C144,C164,C165,C174,C184,C202,C223,C242,C259,C261,C277,C319,C382,C383,C384,C385,C418</t>
+  </si>
+  <si>
+    <t>0010050070</t>
+  </si>
+  <si>
+    <t>C170,C172</t>
+  </si>
+  <si>
+    <t>0010050079</t>
+  </si>
+  <si>
+    <t>C346,C347</t>
+  </si>
+  <si>
+    <t>0010050083</t>
+  </si>
+  <si>
+    <t>C336,C337,C339,C340,C345,C352</t>
+  </si>
+  <si>
+    <t>0010050204</t>
+  </si>
+  <si>
+    <t>C27,C39,C41,C43,C86,C116,C119,C122,C251,C257,C263,C267</t>
+  </si>
+  <si>
+    <t>0010050165</t>
+  </si>
+  <si>
+    <t>C32,C134,C162,C163</t>
+  </si>
+  <si>
+    <t>0010050157</t>
+  </si>
+  <si>
+    <t>C4,C78,C96,C101,C117,C128,C129,C142,C148,C154,C156,C208,C231,C239,C415,C429</t>
+  </si>
+  <si>
+    <t>0010050164</t>
+  </si>
+  <si>
+    <t>C1,C2,C100,C106,C109,C111,C112,C132,C159,C179,C180,C338,C354,C368,C369,C370,C425,C426,C427,C428,EC3</t>
+  </si>
+  <si>
+    <t>0010050118</t>
+  </si>
+  <si>
+    <t>EC11</t>
+  </si>
+  <si>
+    <t>0010050163</t>
+  </si>
+  <si>
+    <t>C363,C364,C378,C379</t>
+  </si>
+  <si>
+    <t>0010050130</t>
+  </si>
+  <si>
+    <t>C362,C377</t>
+  </si>
+  <si>
+    <t>0010050121</t>
+  </si>
+  <si>
+    <t>EC12</t>
+  </si>
+  <si>
+    <t>0010050117</t>
+  </si>
+  <si>
+    <t>C290,EC5</t>
+  </si>
+  <si>
+    <t>0010050128</t>
+  </si>
+  <si>
+    <t>C357,C372,EC10</t>
+  </si>
+  <si>
+    <t>0010050119</t>
+  </si>
+  <si>
+    <t>EC13</t>
+  </si>
+  <si>
+    <t>0010050133</t>
+  </si>
+  <si>
+    <t>C35,C40</t>
+  </si>
+  <si>
+    <t>0010020008</t>
+  </si>
+  <si>
+    <t>D13,D18,D20</t>
+  </si>
+  <si>
+    <t>0010020010</t>
+  </si>
+  <si>
+    <t>D14,D22</t>
+  </si>
+  <si>
+    <t>0010020018</t>
+  </si>
+  <si>
+    <t>D1,D8,D9</t>
+  </si>
+  <si>
+    <t>0010020032</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>0010020092</t>
+  </si>
+  <si>
+    <t>D5,D15</t>
+  </si>
+  <si>
+    <t>0010020068</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>0010020015</t>
+  </si>
+  <si>
+    <t>ED7,ED8,ED11,ED21,ESD15,ESD16</t>
+  </si>
+  <si>
+    <t>0010020017</t>
+  </si>
+  <si>
+    <t>CLEARANCE1,ED1,ED4,ED5,ED6,ED32</t>
+  </si>
+  <si>
+    <t>0010020042</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>0010020056</t>
+  </si>
+  <si>
+    <t>ZD2</t>
+  </si>
+  <si>
+    <t>0010020043</t>
+  </si>
+  <si>
+    <t>ZD5</t>
+  </si>
+  <si>
+    <t>0010020059</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>0010020049</t>
+  </si>
+  <si>
+    <t>ZD3,ZD9,ZD10</t>
+  </si>
+  <si>
+    <t>0010020040</t>
+  </si>
+  <si>
+    <t>ZD1,ZD4,ZD7</t>
+  </si>
+  <si>
+    <t>0010140031</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>0010010327</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>0010010562</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>0010110129</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>0010110179</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>0010110161</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>0010130021</t>
+  </si>
+  <si>
+    <t>LED14,LED17,LED18,LED19,LED20</t>
+  </si>
+  <si>
+    <t>0010060134</t>
+  </si>
+  <si>
+    <t>L19,L21</t>
+  </si>
+  <si>
+    <t>0010060125</t>
+  </si>
+  <si>
+    <t>FB2,FB6,FB9,FB15,FB19,FB23,FB24,FB29,FB30,FB31,FB32,FB34,FB35,FB38,FB45</t>
+  </si>
+  <si>
+    <t>0010060120</t>
+  </si>
+  <si>
+    <t>1N1,FB3,FB4,FB7,FB8,FB10,FB12,FB13,FB17,FB18,FB21,FB22,FB25</t>
+  </si>
+  <si>
+    <t>0010060130</t>
+  </si>
+  <si>
+    <t>FB36,FB39</t>
+  </si>
+  <si>
+    <t>0010060127</t>
+  </si>
+  <si>
+    <t>FB5,FB33,FB40,FB43</t>
+  </si>
+  <si>
+    <t>0010060115</t>
+  </si>
+  <si>
+    <t>FB41,FB42</t>
+  </si>
+  <si>
+    <t>0010060083</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>0010060124</t>
+  </si>
+  <si>
+    <t>FB1,FB16,FB26,FB27</t>
+  </si>
+  <si>
+    <t>0010060155</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>0010060058</t>
+  </si>
+  <si>
+    <t>L2,L5,L17</t>
+  </si>
+  <si>
+    <t>0010060091</t>
+  </si>
+  <si>
+    <t>L20</t>
+  </si>
+  <si>
+    <t>0010060147</t>
+  </si>
+  <si>
+    <t>L16</t>
+  </si>
+  <si>
+    <t>0010060052</t>
+  </si>
+  <si>
+    <t>L9,L10,L11,L12</t>
+  </si>
+  <si>
+    <t>0010060150</t>
+  </si>
+  <si>
+    <t>L3,L4,L6,L7,L8</t>
+  </si>
+  <si>
+    <t>0010010652</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>0010030012</t>
+  </si>
+  <si>
+    <t>Q2,Q4,Q10,Q20,Q27</t>
+  </si>
+  <si>
+    <t>0010010040</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>0010030014</t>
+  </si>
+  <si>
+    <t>Q1,Q3,Q5</t>
+  </si>
+  <si>
+    <t>0010030017</t>
+  </si>
+  <si>
+    <t>Q6,Q11,Q12,Q14,Q15,Q19,Q21,Q22,Q23,Q24,Q25,Q26,Q28</t>
+  </si>
+  <si>
+    <t>0010030019</t>
+  </si>
+  <si>
+    <t>Q7,Q16</t>
+  </si>
+  <si>
+    <t>0010030020</t>
+  </si>
+  <si>
+    <t>Q17</t>
+  </si>
+  <si>
+    <t>0010040319</t>
+  </si>
+  <si>
+    <t>R31,R127,R204,R275</t>
+  </si>
+  <si>
+    <t>0010040329</t>
+  </si>
+  <si>
+    <t>R135</t>
+  </si>
+  <si>
+    <t>0010040458</t>
+  </si>
+  <si>
+    <t>R139</t>
+  </si>
+  <si>
+    <t>0010040447</t>
+  </si>
+  <si>
+    <t>R2,R10,R26,R53,R71,R102,R119,R153,R190,R224,R232,R244,R249,R250,R255,R282,R380</t>
+  </si>
+  <si>
+    <t>0010040323</t>
+  </si>
+  <si>
+    <t>R130,R161,R168,R169,R170,R171,R172,R202,R203,R205,R257,R276,R277,R278,R279,R291,R294,R297,R298,R325,R329,R387,R388</t>
+  </si>
+  <si>
+    <t>0010040337</t>
+  </si>
+  <si>
+    <t>R1,R3,R11,R15,R16,R21,R22,R23,R25,R27,R28,R36,R44,R46,R47,R54,R57,R58,R59,R72,R76,R78,R80,R81,R82,R83,R84,R85,R86,R90,R95,R96,R105,R110,R112,R113,R114,R116,R117,R118,R128,R129,R136,R137,R138,R152,R155,R156,R163,R166,R167,R173,R191,R196,R211,R215,R218,R223,R226,R242,R245,R254,R270,R273,R283,R286,R287,R288,R289,R305,R315,R355,R363,R371,R375,R376,R377,R378,R394,R396,R399,R634</t>
+  </si>
+  <si>
+    <t>0010040360</t>
+  </si>
+  <si>
+    <t>R212,R221</t>
+  </si>
+  <si>
+    <t>0010040353</t>
+  </si>
+  <si>
+    <t>R219</t>
+  </si>
+  <si>
+    <t>0010040354</t>
+  </si>
+  <si>
+    <t>R207,R216,R233,R253</t>
+  </si>
+  <si>
+    <t>0010040339</t>
+  </si>
+  <si>
+    <t>R68,R198,R209,R263,R266,R348,R356,R364,R372</t>
+  </si>
+  <si>
+    <t>0010040364</t>
+  </si>
+  <si>
+    <t>R4,R9,R12,R41,R56,R92,R131,R134,R149,R174,R206,R214,R285,R333,R334,R351,R352,R367,R368,R379,R389,R395,R402,R630</t>
+  </si>
+  <si>
+    <t>0010040332</t>
+  </si>
+  <si>
+    <t>R66,R67,R132,R140,R182,R186,R227,R231,R269,R272,R313,R314</t>
+  </si>
+  <si>
+    <t>0010040320</t>
+  </si>
+  <si>
+    <t>R61,R89,R393</t>
+  </si>
+  <si>
+    <t>0010040390</t>
+  </si>
+  <si>
+    <t>R187,R195,R222,R235,R238,R256,R259,R337,R338,R341,R342,R359,R360,R373,R374,R631</t>
+  </si>
+  <si>
+    <t>0010040321</t>
+  </si>
+  <si>
+    <t>R115</t>
+  </si>
+  <si>
+    <t>0010040326</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>0010040331</t>
+  </si>
+  <si>
+    <t>R247,R248</t>
+  </si>
+  <si>
+    <t>0010040362</t>
+  </si>
+  <si>
+    <t>R400</t>
+  </si>
+  <si>
+    <t>0010040334</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>0010040344</t>
+  </si>
+  <si>
+    <t>R349,R350,R365,R366</t>
+  </si>
+  <si>
+    <t>0010040345</t>
+  </si>
+  <si>
+    <t>R208</t>
+  </si>
+  <si>
+    <t>0010040483</t>
+  </si>
+  <si>
+    <t>R159,R160,R268,R271</t>
+  </si>
+  <si>
+    <t>0010040296</t>
+  </si>
+  <si>
+    <t>R29,R35,R39,R40,R42,R50,R51,R52,R63,R64,R70,R87,R88,R101,R103,R111,R121,R122,R123,R124,R125,R126,R142,R179,R188,R189,R280,R284,R290,R303,R306,R307,R308,R309,R310,R311,R312,R316,R317,R318,R319,R322,R323,R324,R326</t>
+  </si>
+  <si>
+    <t>0010040484</t>
+  </si>
+  <si>
+    <t>R225</t>
+  </si>
+  <si>
+    <t>0010040335</t>
+  </si>
+  <si>
+    <t>R32,R75,R194,R199,R237,R243,R274,R292,R295,R296,R320,R321,R327,R335,R336,R339,R340,R346,R347,R361,R362</t>
+  </si>
+  <si>
+    <t>0010040358</t>
+  </si>
+  <si>
+    <t>R213,R220,R391,R392</t>
+  </si>
+  <si>
+    <t>0010040487</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>0010040359</t>
+  </si>
+  <si>
+    <t>R193</t>
+  </si>
+  <si>
+    <t>0010040459</t>
+  </si>
+  <si>
+    <t>R6,R7,R8,R30,R157,R236,R246,R251,R252,R258,R281,R293</t>
+  </si>
+  <si>
+    <t>0010040472</t>
+  </si>
+  <si>
+    <t>R98,R106</t>
+  </si>
+  <si>
+    <t>0010040473</t>
+  </si>
+  <si>
+    <t>R343,R344</t>
+  </si>
+  <si>
+    <t>0010040348</t>
+  </si>
+  <si>
+    <t>R230</t>
+  </si>
+  <si>
+    <t>0010040461</t>
+  </si>
+  <si>
+    <t>R267</t>
+  </si>
+  <si>
+    <t>0010040460</t>
+  </si>
+  <si>
+    <t>R73,R107,R217</t>
+  </si>
+  <si>
+    <t>0010040350</t>
+  </si>
+  <si>
+    <t>R65,R192,R197</t>
+  </si>
+  <si>
+    <t>0010040322</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>0010040370</t>
+  </si>
+  <si>
+    <t>R264,R265</t>
+  </si>
+  <si>
+    <t>0010040498</t>
+  </si>
+  <si>
+    <t>R133</t>
+  </si>
+  <si>
+    <t>0010040351</t>
+  </si>
+  <si>
+    <t>R109,R210</t>
+  </si>
+  <si>
+    <t>0010040256</t>
+  </si>
+  <si>
+    <t>R5,R37,R38,R69,R74,R79,R175</t>
+  </si>
+  <si>
+    <t>0010040077</t>
+  </si>
+  <si>
+    <t>R18,R77,R143,R144,R145</t>
+  </si>
+  <si>
+    <t>0010040204</t>
+  </si>
+  <si>
+    <t>R20,R91</t>
+  </si>
+  <si>
+    <t>0010040062</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>0010040157</t>
+  </si>
+  <si>
+    <t>R357,R358</t>
+  </si>
+  <si>
+    <t>0010040051</t>
+  </si>
+  <si>
+    <t>R24,R93</t>
+  </si>
+  <si>
+    <t>0010040122</t>
+  </si>
+  <si>
+    <t>R141</t>
+  </si>
+  <si>
+    <t>0010040034</t>
+  </si>
+  <si>
+    <t>R62,R401</t>
+  </si>
+  <si>
+    <t>0010040160</t>
+  </si>
+  <si>
+    <t>R345,R353,R354,R369,R370</t>
+  </si>
+  <si>
+    <t>0010040103</t>
+  </si>
+  <si>
+    <t>R200,R201</t>
+  </si>
+  <si>
+    <t>0010010563</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>0010020072</t>
+  </si>
+  <si>
+    <t>ED38,ED39</t>
+  </si>
+  <si>
+    <t>0010010548</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>0010010219</t>
+  </si>
+  <si>
+    <t>U23</t>
+  </si>
+  <si>
+    <t>0010010607</t>
+  </si>
+  <si>
+    <t>U12,U13</t>
+  </si>
+  <si>
+    <t>0010010304</t>
+  </si>
+  <si>
+    <t>U29</t>
+  </si>
+  <si>
+    <t>0010010085</t>
+  </si>
+  <si>
+    <t>U2,U5</t>
+  </si>
+  <si>
+    <t>0010010103</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>0010010054</t>
+  </si>
+  <si>
+    <t>U904</t>
+  </si>
+  <si>
+    <t>0010010183</t>
+  </si>
+  <si>
+    <t>U9,U16</t>
+  </si>
+  <si>
+    <t>0010010184</t>
+  </si>
+  <si>
+    <t>U21</t>
+  </si>
+  <si>
+    <t>0010060174</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>0010010027</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -42,85 +1210,340 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,52 +1826,1506 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C135"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="36.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>位号</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0010050170</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C84,C167,C171,C310</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="81" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" ht="27" spans="1:3">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" ht="40.5" spans="1:3">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="40.5" spans="1:3">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" spans="1:3">
+      <c r="A54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" ht="27" spans="1:3">
+      <c r="A55" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" ht="27" spans="1:3">
+      <c r="A71" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="40.5" spans="1:3">
+      <c r="A77" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" ht="54" spans="1:3">
+      <c r="A78" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" ht="148.5" spans="1:3">
+      <c r="A79" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" ht="27" spans="1:3">
+      <c r="A83" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" ht="54" spans="1:3">
+      <c r="A84" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" ht="27" spans="1:3">
+      <c r="A85" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" ht="40.5" spans="1:3">
+      <c r="A87" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" ht="94.5" spans="1:3">
+      <c r="A96" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" ht="40.5" spans="1:3">
+      <c r="A98" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" ht="27" spans="1:3">
+      <c r="A102" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C102" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C107" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C110" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C111" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C112" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C113" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C114" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C115" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C117" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C119" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C121" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C122" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C124" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C125" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C129" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C130" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C131" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C134" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C135" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/test_bom_upload.xlsx
+++ b/test_bom_upload.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="14025" windowHeight="9465"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>

--- a/test_bom_upload.xlsx
+++ b/test_bom_upload.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14025" windowHeight="9465"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="271">
   <si>
     <t>物料编码</t>
   </si>
@@ -725,7 +725,7 @@
     <t>R108</t>
   </si>
   <si>
-    <t>0010040157</t>
+    <t>0010090816</t>
   </si>
   <si>
     <t>R357,R358</t>
@@ -837,6 +837,9 @@
   </si>
   <si>
     <t>U26</t>
+  </si>
+  <si>
+    <t>0010090815</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +1835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" customWidth="1"/>
@@ -3324,6 +3327,13 @@
         <v>1</v>
       </c>
     </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" s="2"/>
+      <c r="C136" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
